--- a/Data Files/Backoffce/GestaoVerificacoesAtribuicaoManual/GestaoVerificacoesAtribuicaoManual.xlsx
+++ b/Data Files/Backoffce/GestaoVerificacoesAtribuicaoManual/GestaoVerificacoesAtribuicaoManual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GestaoVerificacoesAtribuicaoManual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Ntxnas1.intrallianz.es\brasil\DIRETORIAS\DIR EXE OPERACOES\DIR TI\SUPERINT DESENV PRODUTOS\RPA\Denilson\EXECUÇÃO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{3C83A80C-E51E-4A86-A264-83B713C82973}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{F1C9FBBA-1613-4710-BB0A-261C8D558A0C}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="1" r:id="rId2" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GestaoVerificacoesAtribuicaoMan!$A$1:$F$53</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GestaoVerificacoesAtribuicaoMan!$A$1:$F$126</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="95">
   <si>
     <t>Status</t>
   </si>
@@ -51,6 +51,9 @@
     <t>NIF</t>
   </si>
   <si>
+    <t>Processar</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -60,15 +63,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
-    <t>17661659000191</t>
-  </si>
-  <si>
-    <t>133805560</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -78,109 +72,250 @@
     <t>6</t>
   </si>
   <si>
-    <t>134688528</t>
-  </si>
-  <si>
-    <t>133474488</t>
-  </si>
-  <si>
-    <t>134722016</t>
-  </si>
-  <si>
-    <t>134036319</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>134234519</t>
-  </si>
-  <si>
-    <t>134093583</t>
-  </si>
-  <si>
-    <t>134643822</t>
-  </si>
-  <si>
-    <t>10/02/2025</t>
-  </si>
-  <si>
-    <t>135403503</t>
-  </si>
-  <si>
-    <t>133938369</t>
-  </si>
-  <si>
-    <t>132679971</t>
-  </si>
-  <si>
-    <t>134524906</t>
-  </si>
-  <si>
-    <t>135461218</t>
-  </si>
-  <si>
-    <t>133004273</t>
-  </si>
-  <si>
-    <t>135352569</t>
-  </si>
-  <si>
-    <t>134388638</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>134267911</t>
-  </si>
-  <si>
-    <t>135476413</t>
-  </si>
-  <si>
-    <t>135387025</t>
-  </si>
-  <si>
-    <t>133442994</t>
-  </si>
-  <si>
-    <t>134640433</t>
+    <t>140927321</t>
+  </si>
+  <si>
+    <t>38292461000158        </t>
+  </si>
+  <si>
+    <t>138687855</t>
+  </si>
+  <si>
+    <t>140881242</t>
+  </si>
+  <si>
+    <t>140962433</t>
+  </si>
+  <si>
+    <t>140969463</t>
+  </si>
+  <si>
+    <t>140570267</t>
+  </si>
+  <si>
+    <t>140815319</t>
+  </si>
+  <si>
+    <t>138982597</t>
+  </si>
+  <si>
+    <t>140381090</t>
+  </si>
+  <si>
+    <t>140886637</t>
+  </si>
+  <si>
+    <t>140970335</t>
+  </si>
+  <si>
+    <t>140778221</t>
+  </si>
+  <si>
+    <t>141033688</t>
+  </si>
+  <si>
+    <t>141040391</t>
+  </si>
+  <si>
+    <t>140639669</t>
+  </si>
+  <si>
+    <t>138984802</t>
+  </si>
+  <si>
+    <t>140918315</t>
+  </si>
+  <si>
+    <t>140960275</t>
+  </si>
+  <si>
+    <t>140898304</t>
+  </si>
+  <si>
+    <t>141082517</t>
+  </si>
+  <si>
+    <t>140956502</t>
+  </si>
+  <si>
+    <t>138427656</t>
+  </si>
+  <si>
+    <t>141075923</t>
+  </si>
+  <si>
+    <t>140484696</t>
+  </si>
+  <si>
+    <t>140855156</t>
+  </si>
+  <si>
+    <t>140751754</t>
+  </si>
+  <si>
+    <t>140748518</t>
+  </si>
+  <si>
+    <t>140446693</t>
+  </si>
+  <si>
+    <t>140987431</t>
+  </si>
+  <si>
+    <t>141048087</t>
+  </si>
+  <si>
+    <t>140891994</t>
+  </si>
+  <si>
+    <t>140924439</t>
+  </si>
+  <si>
+    <t>140971912</t>
+  </si>
+  <si>
+    <t>140880190</t>
+  </si>
+  <si>
+    <t>140880707</t>
+  </si>
+  <si>
+    <t>140486440</t>
+  </si>
+  <si>
+    <t>138779670</t>
+  </si>
+  <si>
+    <t>141101586</t>
+  </si>
+  <si>
+    <t>140930339</t>
+  </si>
+  <si>
+    <t>141131689</t>
+  </si>
+  <si>
+    <t>140165254</t>
+  </si>
+  <si>
+    <t>140972943</t>
+  </si>
+  <si>
+    <t>140158236</t>
+  </si>
+  <si>
+    <t>140494523</t>
+  </si>
+  <si>
+    <t>140947308</t>
+  </si>
+  <si>
+    <t>140855471</t>
+  </si>
+  <si>
+    <t>140910301</t>
+  </si>
+  <si>
+    <t>141120183</t>
+  </si>
+  <si>
+    <t>140356863</t>
+  </si>
+  <si>
+    <t>140020688</t>
+  </si>
+  <si>
+    <t>140664304</t>
+  </si>
+  <si>
+    <t>140897400</t>
+  </si>
+  <si>
+    <t>140956453</t>
+  </si>
+  <si>
+    <t>139014954</t>
+  </si>
+  <si>
+    <t>140976970</t>
+  </si>
+  <si>
+    <t>138997772</t>
+  </si>
+  <si>
+    <t>140544712</t>
+  </si>
+  <si>
+    <t>141103698</t>
+  </si>
+  <si>
+    <t>141029575</t>
+  </si>
+  <si>
+    <t>140454515</t>
+  </si>
+  <si>
+    <t>140455331</t>
+  </si>
+  <si>
+    <t>140945692</t>
+  </si>
+  <si>
+    <t>141081309</t>
+  </si>
+  <si>
+    <t>138277433</t>
+  </si>
+  <si>
+    <t>140847928</t>
+  </si>
+  <si>
+    <t>140673601</t>
+  </si>
+  <si>
+    <t>141086528</t>
+  </si>
+  <si>
+    <t>141083078</t>
+  </si>
+  <si>
+    <t>140352087</t>
+  </si>
+  <si>
+    <t>140956576</t>
+  </si>
+  <si>
+    <t>140885157</t>
+  </si>
+  <si>
+    <t>140750003</t>
+  </si>
+  <si>
+    <t>138915570</t>
+  </si>
+  <si>
+    <t>141114768</t>
   </si>
   <si>
     <t>Processado</t>
   </si>
   <si>
-    <t>atributo nao encontrado</t>
+    <t> Operação efetuada</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao preencher 'GESTÃO DE RECLAMAÇÕES'</t>
   </si>
   <si>
     <t>Alerta:  A apólice não está em vigor</t>
-  </si>
-  <si>
-    <t>Alerta:  01 Data Averiguação *	 Data deve ser igual ou posterior ao dia de hoje
- 02 Cidade	 Campo necessário
- 03 Estado	 Campo necessário</t>
-  </si>
-  <si>
-    <t>Alerta:  01 Data Averiguação *	 Data deve ser igual ou posterior ao dia de hoje
- 02 Telefone 1 *	 Campo necessário</t>
-  </si>
-  <si>
-    <t>Alerta:  01 Data Averiguação *	 Data deve ser igual ou posterior ao dia de hoje</t>
-  </si>
-  <si>
-    <t>Alerta: Falha ao preencher 'GESTÃO DE RECLAMAÇÕES'</t>
-  </si>
-  <si>
-    <t>Alerta:  Existe uma averiguação ativa para esta apólice</t>
   </si>
 </sst>
 </file>
@@ -289,7 +424,7 @@
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="4" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,9 +443,6 @@
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
@@ -634,31 +766,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I202"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" customWidth="true" style="3" width="17.85546875" collapsed="true"/>
     <col min="3" max="3" customWidth="true" style="3" width="16.0" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="3" width="19.42578125" collapsed="true"/>
     <col min="5" max="5" customWidth="true" style="5" width="14.5703125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="7" width="100.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="100.0" collapsed="true"/>
     <col min="7" max="16384" style="4" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row customFormat="1" r="1" s="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -673,19 +805,19 @@
         <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -693,121 +825,121 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
     </row>
-    <row hidden="1" r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -815,19 +947,19 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -835,19 +967,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -855,19 +987,19 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -875,849 +1007,3823 @@
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row hidden="1" r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row hidden="1" r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row hidden="1" r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row hidden="1" r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row hidden="1" r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row hidden="1" r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row hidden="1" r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row hidden="1" r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row hidden="1" r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row hidden="1" r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="C45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row hidden="1" r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row hidden="1" r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row hidden="1" r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="C54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F55" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F63" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F64" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F66" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F84" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F52" t="s">
+      <c r="B85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F87" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F88" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F98" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F99" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row hidden="1" r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="B100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F100" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F102" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F103" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F104" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F105" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F106" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F107" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F108" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F109" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F110" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F111" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F112" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F113" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F114" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F115" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F116" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F117" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F118" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F119" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F120" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F121" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F122" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F123" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F124" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F125" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F126" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F127" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F128" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F129" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F130" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F131" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F132" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F133" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F134" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F135" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F136" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F137" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F138" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F139" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F140" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F141" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F142" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F143" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F144" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F145" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F146" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F147" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F148" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F149" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F150" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F151" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F152" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F153" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F154" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F155" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F156" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F157" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F158" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F159" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F160" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F161" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F162" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F163" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F164" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F165" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F166" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F167" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F168" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F169" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F170" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F171" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F172" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F173" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F174" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F175" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F176" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F177" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F178" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F179" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F180" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F181" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F182" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F183" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F184" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F185" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F186" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F187" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F188" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F189" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F190" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F191" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F192" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F193" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F194" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F195" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F196" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F197" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F198" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F199" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B200" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F53" t="s">
-        <v>46</v>
+      <c r="C200" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F200" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F201" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F202" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F53" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="atributo nao encontrado"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F126" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
   <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
